--- a/UOri/UOri_Producto.xlsx
+++ b/UOri/UOri_Producto.xlsx
@@ -2801,13 +2801,13 @@
         <v>0.01389656398186374</v>
       </c>
       <c r="L2" s="2">
-        <v>112.2262160580291</v>
+        <v>111.2921052077582</v>
       </c>
       <c r="M2" s="2">
-        <v>0.5198529306309549</v>
+        <v>0.5155259535653072</v>
       </c>
       <c r="N2" s="2">
-        <v>0.01559558791892865</v>
+        <v>0.01546577860695921</v>
       </c>
     </row>
     <row r="3" spans="1:14">
